--- a/tiktok/链接.xlsx
+++ b/tiktok/链接.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="19635" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,24 +29,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>链接</t>
   </si>
   <si>
-    <t>https://vt.tiktok.com/ZS968Trhy9Gsd-n7xZl/</t>
+    <t>https://vt.tiktok.com/ZS968TNN3DABc-wfUGE/</t>
+  </si>
+  <si>
+    <t>https://vt.tiktok.com/ZS968TLm1cK6R-Cr07o/</t>
   </si>
   <si>
     <t>https://vt.tiktok.com/ZS968TFKQscPc-PYgca/</t>
   </si>
   <si>
-    <t>https://vt.tiktok.com/ZS968TLm1cK6R-Cr07o/</t>
-  </si>
-  <si>
-    <t>https://vt.tiktok.com/ZS968TNN3DABc-wfUGE/</t>
-  </si>
-  <si>
-    <t>https://vt.tiktok.com/ZS968TdxuEmqb-0d7sQ/</t>
+    <t>https://vt.tiktok.com/ZS968Trhy9Gsd-n7xZl/</t>
   </si>
 </sst>
 </file>
@@ -59,13 +56,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -513,7 +515,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -532,142 +534,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -717,6 +723,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -979,36 +986,37 @@
   <sheetPr/>
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="88.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="2" ht="22" customHeight="1" spans="1:1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" ht="14.25" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="4" ht="14.25" spans="1:1">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="5" ht="14.25" spans="1:1">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
+    <row r="6" ht="14.25" spans="1:1">
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
